--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ManpowerMensal" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usuarios" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4634,4 +4635,285 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>perfil</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>modulos</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>senha_hash</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>senha_salt</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ultimo_login</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>criado_em</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bruno.picinini@3scorporate.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Home|Organograma|KPIs|Controle de Pessoas|Usuarios</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>dd5051cd03aa7c593261beac1c2c0f0eb85666df498e6f70ef59a85c5e4d8207</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>69a01ce5944be39216bce754679ab171</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>46117.54859120164</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gabriel Spohr</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>gabriel.spohr@3scorporate.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Usuário</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Home|Organograma|KPIs|Controle de Pessoas</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0f051909c5bd0a0390c42c64619393fb26b9790b7deb2ac6150e1fe830cd4e97</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>17fe3572b51abe7b1929f2a7ddca700f</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>46117.54859202715</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Celso Petry</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>celso.petry@3scorporate.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Usuário</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Home|Organograma|KPIs|Controle de Pessoas</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4cbfe98aeeb6c33d4000027df45bffe143f4bf5399abfea816eb6cd98ac5343e</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>734d5890d05d24730dc4b8dd345bfd21</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>46117.54859297851</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Patrice Basso</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>patrice.basso@3scorporate.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Usuário</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Home|Organograma|KPIs|Controle de Pessoas</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>071474ac2e110da8d05bff4b46e2dd846dd16220f4bf9455189120cc29455835</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7d86dbddb70dbd4f28f4304f389e03e2</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>46117.54859405576</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gabriel Hilgert</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>gabriel.hilgert@leaderlog.com.br</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Usuário</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Home|Organograma|KPIs|Controle de Pessoas</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7030eefa97248ba88cdb7cfb8baed5b17bb93176e26c60e8ec248e9bd0a62068</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7ba08a1bf42d9c0f7d607f6590a080c2</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>46117.54859490817</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -4737,8 +4737,11 @@
           <t>69a01ce5944be39216bce754679ab171</t>
         </is>
       </c>
+      <c r="I2" s="2" t="n">
+        <v>46123.92182275392</v>
+      </c>
       <c r="J2" s="2" t="n">
-        <v>46117.54859120164</v>
+        <v>46117.5485912037</v>
       </c>
     </row>
     <row r="3">
@@ -4781,7 +4784,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46117.54859202715</v>
+        <v>46117.54859202547</v>
       </c>
     </row>
     <row r="4">
@@ -4824,7 +4827,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46117.54859297851</v>
+        <v>46117.54859297453</v>
       </c>
     </row>
     <row r="5">
@@ -4867,7 +4870,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46117.54859405576</v>
+        <v>46117.54859405092</v>
       </c>
     </row>
     <row r="6">
@@ -4910,7 +4913,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46117.54859490817</v>
+        <v>46117.54859490741</v>
       </c>
     </row>
   </sheetData>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -1,18 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departamentos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colaboradores" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ManpowerMensal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Departamentos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cargos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Colaboradores" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Historico" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ManpowerMensal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Performance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Usuarios" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4634,4 +4635,285 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>perfil</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>modulos</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>senha_hash</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>senha_salt</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ultimo_login</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>criado_em</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bruno.picinini@3scorporate.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Home|Organograma|KPIs|Controle de Pessoas|Usuarios</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>7d493b1067ee245e0b36da8e45de1b062c1494bfaf976192bd870aaf2757ea78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>d9e103d9b9e10f1c5364b5410a58c48e</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>46124.81842817014</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gabriel Spohr</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>gabriel.spohr@3scorporate.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Usuário</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Home|Organograma|KPIs|Controle de Pessoas</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>d450db50d7e0b3fad4ce3572f6b0868d2610a04b4fe6363b6c9835d83ec40158</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>f572c3f99bebad8653705482bfce3b7d</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>46124.81842873771</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Celso Petry</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>celso.petry@3scorporate.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Usuário</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Home|Organograma|KPIs|Controle de Pessoas</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3a9d9c02120bdb6eac262e8eb5e00c211567354dd598d44d23312cc8b5da3144</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>48b68ccf44f360c22eee7cf25f0af6d8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>46124.81842928693</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Patrice Basso</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>patrice.basso@3scorporate.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Usuário</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Home|Organograma|KPIs|Controle de Pessoas</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>311db00720ceb4b5b5525f58437c529113bb0b01fab62fe110d86091e9a3b75c</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>89300e0e6f36bd78171f437b0358b1cb</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>46124.81842984216</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gabriel Hilgert</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>gabriel.hilgert@leaderlog.com.br</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Usuário</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Home|Organograma|KPIs|Controle de Pessoas</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2b84edfc286b423959a631024a38919aa4c0e2c04572e471f074ea590a44d16e</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5c852f977b3fb0493bb1fe706250d6f0</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>46124.81843038776</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -4737,8 +4737,11 @@
           <t>d9e103d9b9e10f1c5364b5410a58c48e</t>
         </is>
       </c>
+      <c r="I2" s="2" t="n">
+        <v>46124.94644864728</v>
+      </c>
       <c r="J2" s="2" t="n">
-        <v>46124.81842817014</v>
+        <v>46124.8184281713</v>
       </c>
     </row>
     <row r="3">
@@ -4781,7 +4784,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46124.81842873771</v>
+        <v>46124.81842873843</v>
       </c>
     </row>
     <row r="4">
@@ -4824,7 +4827,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46124.81842928693</v>
+        <v>46124.81842928241</v>
       </c>
     </row>
     <row r="5">
@@ -4867,7 +4870,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46124.81842984216</v>
+        <v>46124.81842983796</v>
       </c>
     </row>
     <row r="6">
@@ -4910,7 +4913,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46124.81843038776</v>
+        <v>46124.81843039352</v>
       </c>
     </row>
   </sheetData>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46124.94644864728</v>
+        <v>46125.51720436838</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46125.51720436838</v>
+        <v>46125.51720436342</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>
@@ -4911,6 +4911,9 @@
         <is>
           <t>5c852f977b3fb0493bb1fe706250d6f0</t>
         </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>46125.52624350946</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>46124.81843039352</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46125.51720436342</v>
+        <v>46125.70025250642</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46125.52624350946</v>
+        <v>46125.52624350695</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>46124.81843039352</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departamentos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colaboradores" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ManpowerMensal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usuarios" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Departamentos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cargos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Colaboradores" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Historico" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ManpowerMensal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Performance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Usuarios" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4643,7 +4643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46117.54859120164</v>
+        <v>46117.5485912037</v>
       </c>
     </row>
     <row r="3">
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46117.54859202715</v>
+        <v>46117.54859202547</v>
       </c>
     </row>
     <row r="4">
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46117.54859297851</v>
+        <v>46117.54859297453</v>
       </c>
     </row>
     <row r="5">
@@ -4858,16 +4858,16 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>071474ac2e110da8d05bff4b46e2dd846dd16220f4bf9455189120cc29455835</t>
+          <t>87e00b564aa646be53283ed07e8dbbdea91be2e3a467cf9f795f0047d89c46f5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7d86dbddb70dbd4f28f4304f389e03e2</t>
+          <t>f05f42a7d18a07cbdfd07cb9824ae830</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46117.54859405576</v>
+        <v>46117.54859405092</v>
       </c>
     </row>
     <row r="6">
@@ -4910,7 +4910,50 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46117.54859490817</v>
+        <v>46117.54859490741</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Mariana Strick</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mariana.strick@3scorporate.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Usuário</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Home|Organograma|KPIs|Controle de Pessoas</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>dc7512ab5e55034dbef89d79725b739292a14be4bcb78fc287572760f5b2fc37</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>a36f8938d3c60325f900d0389ed23b85</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>46125.71692149327</v>
       </c>
     </row>
   </sheetData>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1042,6 +1042,11 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>responsavel_direto</t>
         </is>
       </c>
     </row>
@@ -4958,8 +4963,11 @@
           <t>6711d8f4da81bca2eec52db48ca8635d</t>
         </is>
       </c>
+      <c r="I7" s="2" t="n">
+        <v>46125.75542986592</v>
+      </c>
       <c r="J7" s="2" t="n">
-        <v>46125.72053206885</v>
+        <v>46125.72053207176</v>
       </c>
     </row>
   </sheetData>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -2891,6 +2891,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Camila de Souza Nunes</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4964,7 +4969,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46125.75542986592</v>
+        <v>46125.75542986111</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>46125.72053207176</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46125.75542986111</v>
+        <v>46125.81147603361</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>46125.72053207176</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -1793,6 +1793,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Nicoly Cordeiro Lins</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4969,7 +4974,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46125.81147603361</v>
+        <v>46125.8114760301</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>46125.72053207176</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -2979,6 +2979,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Caroline Florêncio de Andrade</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -3218,6 +3218,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Nicoly Cordeiro Lins</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -3023,6 +3023,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Franciely Meirelles Artigas</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -3306,6 +3306,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Aline Grimm</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -4904,6 +4904,9 @@
           <t>c154e2d95cdf19b280bb9593d2f3f424</t>
         </is>
       </c>
+      <c r="I5" s="2" t="n">
+        <v>46125.92561199656</v>
+      </c>
       <c r="J5" s="2" t="n">
         <v>46124.81842983796</v>
       </c>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -2940,6 +2940,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Camilli Diovana da Silveira</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4905,7 +4910,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46125.92561199656</v>
+        <v>46125.92561200231</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>46124.81842983796</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -1915,6 +1915,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Renan Gomes Dias</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -1876,6 +1876,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Adir Gomes Carvalho</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -2003,6 +2003,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Tainá da Silva Ripcke</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -3087,6 +3087,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Adir Gomes Carvalho</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -1637,6 +1637,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Adir Gomes Carvalho</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -3094,7 +3094,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Adir Gomes Carvalho</t>
+          <t>Tainá da Silva Ripcke</t>
         </is>
       </c>
     </row>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -3297,6 +3297,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Giovanna Vitória Sebben</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,6 +972,22 @@
       </c>
       <c r="E26" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>100</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Coordenador</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1765,7 +1781,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -1832,6 +1848,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1944,9 +1965,12 @@
       <c r="I24" s="1" t="n">
         <v>43831</v>
       </c>
+      <c r="J24" s="1" t="n">
+        <v>46125</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2965,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
@@ -3182,12 +3206,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Itajaí</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Itajaí</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3433,6 +3457,45 @@
         <v>44669</v>
       </c>
       <c r="K62" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>100</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Novo Hamburgo</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Novo Hamburgo</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>Ativo</t>
         </is>
@@ -3449,7 +3512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4101,6 +4164,37 @@
       </c>
       <c r="F26" s="1" t="n">
         <v>45505</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>23</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Vitória Ayres de Souza</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Desligamento</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Assistente</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Desligamento registrado em 13/04/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4114,7 +4208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4137,6 +4231,62 @@
         <is>
           <t>manpower_total</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -4964,7 +5114,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46125.75542986592</v>
+        <v>46125.75542986111</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>46125.72053207176</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -1653,6 +1653,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Adir Gomes Carvalho</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1809,6 +1814,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Nicoly Cordeiro Lins</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1892,6 +1902,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Adir Gomes Carvalho</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1931,6 +1946,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Renan Gomes Dias</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2012,6 +2032,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Tainá da Silva Ripcke</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2954,6 +2979,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Camilli Diovana da Silveira</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2993,6 +3023,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Caroline Florêncio de Andrade</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3032,6 +3067,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Franciely Meirelles Artigas</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3071,6 +3111,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Tainá da Silva Ripcke</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3227,6 +3272,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Nicoly Cordeiro Lins</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3266,6 +3316,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Giovanna Vitória Sebben</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3303,6 +3358,11 @@
       <c r="K58" t="inlineStr">
         <is>
           <t>Ativo</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Aline Grimm</t>
         </is>
       </c>
     </row>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -3212,12 +3212,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Itajaí</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Itajaí</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Itajaí</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Itajaí</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46125.70025251157</v>
+        <v>46126.71182829039</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46126.71182829039</v>
+        <v>46126.7937557093</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46126.7937557093</v>
+        <v>46127.51410489736</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46127.51410489736</v>
+        <v>46127.62355958385</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -1897,6 +1897,9 @@
       <c r="I22" s="1" t="n">
         <v>43831</v>
       </c>
+      <c r="J22" s="1" t="n">
+        <v>46054</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Ativo</t>
@@ -3244,7 +3247,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
@@ -3572,7 +3575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4254,6 +4257,37 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>Desligamento registrado em 13/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>21</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lívia Moehlecke Haubert</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Licença Maternidade</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Assistente</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Licença maternidade a partir de fevereiro/2026</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4304,7 +4338,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>24.8</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="3">
@@ -4347,6 +4381,48 @@
       </c>
       <c r="D5" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>24.55</v>
       </c>
     </row>
   </sheetData>
@@ -4789,16 +4865,16 @@
         <v>10721</v>
       </c>
       <c r="D20" t="n">
-        <v>24.3</v>
+        <v>24.8</v>
       </c>
       <c r="E20" t="n">
-        <v>441.19</v>
+        <v>432.3</v>
       </c>
       <c r="F20" t="n">
         <v>361.42</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2207</v>
+        <v>1.1961</v>
       </c>
     </row>
     <row r="21">
@@ -4812,16 +4888,16 @@
         <v>10040</v>
       </c>
       <c r="D21" t="n">
-        <v>24.3</v>
+        <v>24.55</v>
       </c>
       <c r="E21" t="n">
-        <v>413.17</v>
+        <v>408.96</v>
       </c>
       <c r="F21" t="n">
         <v>361.42</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1432</v>
+        <v>1.1315</v>
       </c>
     </row>
     <row r="22">
@@ -4835,16 +4911,16 @@
         <v>10700</v>
       </c>
       <c r="D22" t="n">
-        <v>24.3</v>
+        <v>24.55</v>
       </c>
       <c r="E22" t="n">
-        <v>440.33</v>
+        <v>435.85</v>
       </c>
       <c r="F22" t="n">
         <v>361.42</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2183</v>
+        <v>1.2059</v>
       </c>
     </row>
   </sheetData>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46125.70025251157</v>
+        <v>46128.59709076166</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -972,6 +972,22 @@
       </c>
       <c r="E26" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>100</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Coordenador</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -985,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,6 +1060,11 @@
           <t>status</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>responsavel_direto</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1632,6 +1653,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Adir Gomes Carvalho</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1760,7 +1786,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -1786,6 +1812,11 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>Ativo</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Nicoly Cordeiro Lins</t>
         </is>
       </c>
     </row>
@@ -1827,6 +1858,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1861,9 +1897,17 @@
       <c r="I22" s="1" t="n">
         <v>43831</v>
       </c>
+      <c r="J22" s="1" t="n">
+        <v>46054</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Ativo</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Adir Gomes Carvalho</t>
         </is>
       </c>
     </row>
@@ -1905,6 +1949,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Renan Gomes Dias</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1939,9 +1988,12 @@
       <c r="I24" s="1" t="n">
         <v>43831</v>
       </c>
+      <c r="J24" s="1" t="n">
+        <v>46125</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Ativo</t>
+          <t>Inativo</t>
         </is>
       </c>
     </row>
@@ -1983,6 +2035,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Tainá da Silva Ripcke</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2925,6 +2982,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Camilli Diovana da Silveira</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2936,7 +2998,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
         <v>1</v>
@@ -2962,6 +3024,11 @@
       <c r="K50" t="inlineStr">
         <is>
           <t>Ativo</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Caroline Florêncio de Andrade</t>
         </is>
       </c>
     </row>
@@ -3003,6 +3070,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Franciely Meirelles Artigas</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3042,6 +3114,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Tainá da Silva Ripcke</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3138,12 +3215,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Itajaí</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Itajaí</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3170,19 +3247,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Itajaí</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Itajaí</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3196,6 +3273,11 @@
       <c r="K56" t="inlineStr">
         <is>
           <t>Ativo</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Nicoly Cordeiro Lins</t>
         </is>
       </c>
     </row>
@@ -3237,6 +3319,11 @@
           <t>Ativo</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Giovanna Vitória Sebben</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3255,12 +3342,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Itajaí</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Novo Hamburgo</t>
+          <t>Itajaí</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3274,6 +3361,11 @@
       <c r="K58" t="inlineStr">
         <is>
           <t>Ativo</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Aline Grimm</t>
         </is>
       </c>
     </row>
@@ -3428,6 +3520,45 @@
         <v>44669</v>
       </c>
       <c r="K62" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>100</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Novo Hamburgo</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Novo Hamburgo</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>43831</v>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>Ativo</t>
         </is>
@@ -3444,7 +3575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4096,6 +4227,68 @@
       </c>
       <c r="F26" s="1" t="n">
         <v>45505</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>23</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Vitória Ayres de Souza</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Desligamento</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Assistente</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Desligamento registrado em 13/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>21</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lívia Moehlecke Haubert</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Licença Maternidade</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Assistente</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Licença maternidade a partir de fevereiro/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4109,7 +4302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4132,6 +4325,104 @@
         <is>
           <t>manpower_total</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>24.55</v>
       </c>
     </row>
   </sheetData>
@@ -4574,16 +4865,16 @@
         <v>10721</v>
       </c>
       <c r="D20" t="n">
-        <v>24.3</v>
+        <v>24.8</v>
       </c>
       <c r="E20" t="n">
-        <v>441.19</v>
+        <v>432.3</v>
       </c>
       <c r="F20" t="n">
         <v>361.42</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2207</v>
+        <v>1.1961</v>
       </c>
     </row>
     <row r="21">
@@ -4597,16 +4888,16 @@
         <v>10040</v>
       </c>
       <c r="D21" t="n">
-        <v>24.3</v>
+        <v>24.55</v>
       </c>
       <c r="E21" t="n">
-        <v>413.17</v>
+        <v>408.96</v>
       </c>
       <c r="F21" t="n">
         <v>361.42</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1432</v>
+        <v>1.1315</v>
       </c>
     </row>
     <row r="22">
@@ -4620,16 +4911,16 @@
         <v>10700</v>
       </c>
       <c r="D22" t="n">
-        <v>24.3</v>
+        <v>24.55</v>
       </c>
       <c r="E22" t="n">
-        <v>440.33</v>
+        <v>435.85</v>
       </c>
       <c r="F22" t="n">
         <v>361.42</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2183</v>
+        <v>1.2059</v>
       </c>
     </row>
   </sheetData>
@@ -4729,16 +5020,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>dd5051cd03aa7c593261beac1c2c0f0eb85666df498e6f70ef59a85c5e4d8207</t>
+          <t>7d493b1067ee245e0b36da8e45de1b062c1494bfaf976192bd870aaf2757ea78</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>69a01ce5944be39216bce754679ab171</t>
-        </is>
+          <t>d9e103d9b9e10f1c5364b5410a58c48e</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>46125.70025251157</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46117.5485912037</v>
+        <v>46124.8184281713</v>
       </c>
     </row>
     <row r="3">
@@ -4772,16 +5066,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0f051909c5bd0a0390c42c64619393fb26b9790b7deb2ac6150e1fe830cd4e97</t>
+          <t>f5475e4f01c99383d556e136f6e39d86ac1f56e3dc60aaf9785564f4bb2841cb</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>17fe3572b51abe7b1929f2a7ddca700f</t>
+          <t>98ebabb0f0573edc5608e57f38750b71</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46117.54859202547</v>
+        <v>46124.81842873843</v>
       </c>
     </row>
     <row r="4">
@@ -4815,16 +5109,16 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4cbfe98aeeb6c33d4000027df45bffe143f4bf5399abfea816eb6cd98ac5343e</t>
+          <t>3a9d9c02120bdb6eac262e8eb5e00c211567354dd598d44d23312cc8b5da3144</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>734d5890d05d24730dc4b8dd345bfd21</t>
+          <t>48b68ccf44f360c22eee7cf25f0af6d8</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46117.54859297453</v>
+        <v>46124.81842928241</v>
       </c>
     </row>
     <row r="5">
@@ -4858,16 +5152,16 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>87e00b564aa646be53283ed07e8dbbdea91be2e3a467cf9f795f0047d89c46f5</t>
+          <t>614337471b1bdf0d0b1a48d20789ae601814503b33f3c177f28741c14b4af13f</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>f05f42a7d18a07cbdfd07cb9824ae830</t>
+          <t>c154e2d95cdf19b280bb9593d2f3f424</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46117.54859405092</v>
+        <v>46124.81842983796</v>
       </c>
     </row>
     <row r="6">
@@ -4901,16 +5195,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7030eefa97248ba88cdb7cfb8baed5b17bb93176e26c60e8ec248e9bd0a62068</t>
+          <t>2b84edfc286b423959a631024a38919aa4c0e2c04572e471f074ea590a44d16e</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7ba08a1bf42d9c0f7d607f6590a080c2</t>
-        </is>
+          <t>5c852f977b3fb0493bb1fe706250d6f0</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>46125.52624350695</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46117.54859490741</v>
+        <v>46124.81843039352</v>
       </c>
     </row>
     <row r="7">
@@ -4944,16 +5241,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>dc7512ab5e55034dbef89d79725b739292a14be4bcb78fc287572760f5b2fc37</t>
+          <t>62432098e81097f3c7f97cce115ff1875626d0c77b09a94511959b7f73226e5a</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>a36f8938d3c60325f900d0389ed23b85</t>
-        </is>
+          <t>6711d8f4da81bca2eec52db48ca8635d</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>46125.75542986111</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46125.71692149327</v>
+        <v>46125.72053207176</v>
       </c>
     </row>
   </sheetData>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -5074,6 +5074,9 @@
           <t>98ebabb0f0573edc5608e57f38750b71</t>
         </is>
       </c>
+      <c r="I3" s="2" t="n">
+        <v>46128.70413718931</v>
+      </c>
       <c r="J3" s="2" t="n">
         <v>46124.81842873843</v>
       </c>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -14,6 +14,8 @@
     <sheet name="ManpowerMensal" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Performance" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Usuarios" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Restituicoes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="RestituicoesLog" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5075,7 +5077,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46128.70413718931</v>
+        <v>46128.7041371875</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>46124.81842873843</v>
@@ -5257,6 +5259,168 @@
       </c>
       <c r="J7" s="2" t="n">
         <v>46125.72053207176</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>numero_processo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cliente</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cnpj</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>processo_ecac</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>divisao</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>desencaixe</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>valor_principal</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>valor_corrigido</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>responsavel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_protocolo</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>data_retificacao</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>motivo_retificacao</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>termo_assinado</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prazo_fatal</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>criado_em</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>criado_por</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>atualizado_em</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>atualizado_por</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>restituicao_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>data_hora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -5272,7 +5272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5374,6 +5374,3332 @@
       <c r="T1" t="inlineStr">
         <is>
           <t>atualizado_por</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OE1260/24</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Intimação Respondida</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>11000.749726/2024-46</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>12540.83</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>45548</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OE0950/24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Intimação Respondida</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>11000.749725/2024-00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>43837</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>45460</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>45421</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Fatura Comercial desacordo</t>
+        </is>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>OC1262/24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Winning Plastics</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>13352623000256</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Intimação Respondida</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10900-728.384/2024-14</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>464.12</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>45481</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OE1248/23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>IBR DI 24/0157048-8</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>13352623/0003-37</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Intimação Respondida</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10200.722348/2024-34</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>40647.65</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>45313</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Correção de benefício tributário</t>
+        </is>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>610/22</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DAKEN CO3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>44026439000169</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Judicializado</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10983.727889/2024-99</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>8172.94</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>45370</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>44900</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Reclassificação Fiscal/Descrição incompleta</t>
+        </is>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OE0162/23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BRASUTURE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Judicializado</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>11000-747.536/2024-94</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>11499</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Correção de benefício tributário</t>
+        </is>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OP1261/23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MEGA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Judicializado</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>11000-747.535/2024-40</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3169</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Sem exigência - Desembaraço após analise RFB</t>
+        </is>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OE1599/24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>13352623000256</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Judicializado</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>11000-748.922/2024-01</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>458.6</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>45555</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12744/24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>WINNING/VOLCOM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Deferido</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10900.720408/2025-78</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>991.95</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>45681</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>45610</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Reclassificação Fiscal/Descrição incompleta</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4720/22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BRUSTEC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>09019836000102</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Deferido</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>13971.721338/2024-49</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3127.82</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>45370</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>45100</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Reclassificação Fiscal/Descrição incompleta</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>851/26</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R BRANDS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>13992333000196</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10906.135119/2026-08</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>33498.89</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Mariana Strick</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>DUIMP registrada com CE Mercante incorreto, precisou ser cancelada. PIS e COFINS cliente irá se creditar, mas II através de restituição.</t>
+        </is>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1472/23 / MAHINDRA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>13033.211271/2023-58</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>13747</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>45167</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Correção de benefício tributário</t>
+        </is>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1480/23 / MAHINDRA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>13033.211053/2023-13</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>14450</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>45167</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>45072</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Correção de benefício tributário</t>
+        </is>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3955/22</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MAHINDRA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>13033.285961/2022-62</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>14861</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>44879</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>44879</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Correção de benefício tributário</t>
+        </is>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4675/22</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>USARE CO3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>07768403000124</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>10983.728168/2024-04</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>936.4400000000001</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>44981</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>44953</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Reclassificação Fiscal/Descrição incompleta</t>
+        </is>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>853/22</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DAKEN CO3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>44026439000169</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10900.728.344/2024-72</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>8388</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>45370</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>44949</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Reclassificação Fiscal/Descrição incompleta</t>
+        </is>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>OC0974/24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Julian</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>34359845000190</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>10900-729.143/2024-92</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>12054</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>45555</v>
+      </c>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11675/24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Cortexa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>30811836000137</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>11000.751790/2024-97</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>4382.27</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>45621</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>45618</v>
+      </c>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1923/23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Eliseu Kopp</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>93315190000621</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>13033.043781/2024-77</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>22008.5</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M20" s="1" t="n">
+        <v>45121</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Reclassificação Fiscal/Descrição incompleta</t>
+        </is>
+      </c>
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2278/25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Palagi</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>06130052000169</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>11000.734163/2025-72</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>27607.59</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M21" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>70/25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sankem</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>14444651000185</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>11000-735.982/2025-37</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1011.81</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>45845</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2443/25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Infortel</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>87024022000170</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>11000.735756/202-56</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>4175.42</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>45825</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Divergência de volumes</t>
+        </is>
+      </c>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>10529/24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Aplinta</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>40660226000133</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>13033.288833/2024-32</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1233.99</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>45618</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>45583</v>
+      </c>
+      <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2003/25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SGS POLIMEROS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>06355038000163</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>11000.745936/2025-46</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>34414.57</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>45936</v>
+      </c>
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OC0708/23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>UNIPELLI 00.596.161/0005-13</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00596161000190</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>11000-749.101/2024-84</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>6922</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>45149</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Fatura Comercial desacordo</t>
+        </is>
+      </c>
+      <c r="O26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1630/25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>17804883000195</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>11000-741.569/2025-10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1357.38</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Reclassificação Fiscal/Descrição incompleta</t>
+        </is>
+      </c>
+      <c r="O27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OE1260/24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BLK NACIO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>11000.733603/2025-74</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>12540.83</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>45800</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>45548</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Fatura Comercial desacordo</t>
+        </is>
+      </c>
+      <c r="O28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>8594/24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CO3 - DAKEN -</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>44026439000169</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>10900.728.343/2024-28</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>746.8200000000001</v>
+      </c>
+      <c r="O29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>13193/24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>KAZANGIL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>11000.733274/2025-61</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>48267.96</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>45796</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>45785</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Fatura Comercial desacordo</t>
+        </is>
+      </c>
+      <c r="O30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1360/25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>17804883000195</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>11000-741.569/2025-10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1357</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Reclassificação Fiscal/Descrição incompleta</t>
+        </is>
+      </c>
+      <c r="O31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>13068/24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>STRA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>11388997000115</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>10900723560/2025-11</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>20064.71</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>45694</v>
+      </c>
+      <c r="O32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5953/25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>STRA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>11388997000115</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>10900-720.123/2026-18.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>11244.94</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>46028</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Descrição desacordo</t>
+        </is>
+      </c>
+      <c r="O33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>3831/25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>QUALYBESS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Protocolado</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>10900.725822/2025-73</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>909.16</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="O34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>OC0348/23</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MH 30.511.579/0001-18</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>30511579000118</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Com Pendências</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>AG ECAC. 14/10 CHamado CS</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>5332</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M35" s="1" t="n">
+        <v>45050</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Fatura Comercial desacordo</t>
+        </is>
+      </c>
+      <c r="O35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>OE2213/23</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>INSTRUSUL</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Com Pendências</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>2216.36</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>45457</v>
+      </c>
+      <c r="O36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>OE1517/24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BLK</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Deferido</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>11000.749727/2024-91</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1623.8</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1956.5</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="L37" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OP0703/24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EDEGILDO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Deferido</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11000.749724/2024-57</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>36755</v>
+      </c>
+      <c r="J38" t="n">
+        <v>45540.56</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="L38" s="1" t="n">
+        <v>45460</v>
+      </c>
+      <c r="M38" s="1" t="n">
+        <v>45421</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Valor do Seguro errado</t>
+        </is>
+      </c>
+      <c r="O38" t="b">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>OP0696/24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EDEGILDO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Deferido</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>11000.749728/2024-35</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>51258</v>
+      </c>
+      <c r="J39" t="n">
+        <v>63509.24</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="L39" s="1" t="n">
+        <v>45460</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>45421</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Valor do Seguro errado</t>
+        </is>
+      </c>
+      <c r="O39" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OE0710/24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MDC MAX</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Deferido</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>11000.748062/2024-06</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1351.13</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1448.89</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M40" s="1" t="n">
+        <v>45386</v>
+      </c>
+      <c r="O40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OE0949/24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TATAY</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Deferido</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>11000.749729/2024-80</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>3386</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4196.18</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="L41" s="1" t="n">
+        <v>45460</v>
+      </c>
+      <c r="M41" s="1" t="n">
+        <v>45420</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Valor do Seguro errado</t>
+        </is>
+      </c>
+      <c r="O41" t="b">
+        <v>0</v>
+      </c>
+      <c r="P41" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>291/22</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>13352623/000256</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Indeferido</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>10900-729.220/2024-12</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>4004</v>
+      </c>
+      <c r="M42" s="1" t="n">
+        <v>44868</v>
+      </c>
+      <c r="O42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>322/25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Winning (academia)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>13352623000256</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Indeferido</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>11000.721307/2025-21</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>11562.6</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M43" s="1" t="n">
+        <v>45685</v>
+      </c>
+      <c r="O43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>OE0173/23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MONTENGEL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Indeferido</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>11000.747.332/2024-53</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>691</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M44" s="1" t="n">
+        <v>44994</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Fatura Comercial desacordo</t>
+        </is>
+      </c>
+      <c r="O44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>OE1752/23</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MAVE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>13352623000175</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Indeferido</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>11000-752.262/2024-55</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Winning</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>3619.66</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Patrice Zeidler Basso</t>
+        </is>
+      </c>
+      <c r="M45" s="1" t="n">
+        <v>45404</v>
+      </c>
+      <c r="O45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
         </is>
       </c>
     </row>
@@ -5388,7 +8714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5423,6 +8749,3226 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Processo OE1260/24 importado com status 'Intimação Respondida'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>26/12/25: EM 02/12/25 docs juntados pela RFB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Observação: Não temos contrato de câmbio, sendo assim processo 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Processo OE0950/24 importado com status 'Intimação Respondida'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>protocolo (1).pdf 29/12/25: Intimação respondida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Processo OC1262/24 importado com status 'Intimação Respondida'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>18/03/26: Ajustado requerimento para dados Winning 0001.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Processo OE1248/23 importado com status 'Intimação Respondida'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>18/03/2026: Intimação respondida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Processo 610/22 importado com status 'Judicializado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>26/12/25: ARQUIVADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Observação: Encaminhado no dia 19/03/24 para DTCREDITORIO-SAATA-ALF-ITJ-SC - Verificar instrução processual e cadastrar no Sief.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Processo OE0162/23 importado com status 'Judicializado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Em18/03: 18/02/26: distribuido RS-ALF-POA-SADAD-EAD2-GABIN / Gabinete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Observação: Recolhido IPI&lt;  e não era necessário</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Processo OP1261/23 importado com status 'Judicializado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Em 18/03: 16/10/24 distribuido PR-ALF-FOZ-SEDAD-PSFI / Eq de Despacho do PSFI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Observação: Solicitar restituição</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Processo OE1599/24 importado com status 'Judicializado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>18/03/26: Em 04/11/25 SC-ALF-ITJ-SAATA-DTCREDITORIO / Eq Retif</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Observação: Retificação FOB e Frete na nacionalizaçãod e entreposto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Processo 12744/24 importado com status 'Deferido'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>18/03 - Processo DEFERIDO. Aguardando pagamento.   10900720408202578_0000124_0000125_DESPACHO_DECISORIO_20260318_095943.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>10</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Processo 4720/22 importado com status 'Deferido'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>26/12/25: 19.03.24. Reconhecido direito a credito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Observação: seguir com a retificação do item 72347, na invoice 5242, o mesmo foi registrado a NCM errada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>11</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Processo 851/26 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Observação: DUIMP registrada com CE Mercante incorreto, precisou ser cancelada. PIS e COFINS cliente irá se creditar, mas II através de restituição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>12</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Processo 1472/23 / MAHINDRA importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Aguardando retorno da Cláudia Grün referente ao pedido de compensação via PerdComp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Observação: Aguardando prosseguimento no Reconhecimento de Direito Creditório.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>13</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Processo 1480/23 / MAHINDRA importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>13</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Aguardando retorno da Cláudia Grün referente ao pedido de compensação via PerdComp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>13</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Observação: Aguardando prosseguimento no Reconhecimento de Direito Creditório.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>14</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Processo 3955/22 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>14</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Aguardando retorno da Cláudia Grün referente ao pedido de compensação via PerdComp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>14</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Observação: RS-ALF-RGE-SADAD-EQPROC / Eq Analise de Processos  Emitir Parecer / Despacho</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>15</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Processo 4675/22 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>15</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>26/12/25: ARQUIVADO. REABRIR?</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>15</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Observação: Encaminhado no dia 19/03/24 para DTCREDITORIO-SAATA-ALF-ITJ-SC - Verificar instrução processual e cadastrar no Sief.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>16</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Processo 853/22 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>16</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>26/12/25: EM 04/11 direcionado ao setor DTCREDITORIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>16</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Observação: SC-ALF-ITJ-SAATA / Seçao Assessoramento Técnico Aduaneiro - Apreciar e Assinar Documento</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>17</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Processo OC0974/24 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>17</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>29/12/25: 02/12/25 direcionado ao setor DTCREDITORIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>17</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Observação: Di  retificada, após exigência da RFB para alterar NCM.Nova NCM IPI 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>18</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Processo 11675/24 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="n">
+        <v>18</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>29/12/25: Desde 29/09/25 Preparar Distribuição</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="n">
+        <v>18</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Observação: Di registrada com fatura desatualizada. Nova fatura com valores menores. Retificada, e diferença cobrada do cliente, pois restituição será na conta do cliente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="n">
+        <v>19</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Processo 1923/23 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="n">
+        <v>19</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>29/12/25: Desde 18/08/25 setor para Emitir Parecer / Despacho</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="n">
+        <v>20</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Processo 2278/25 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="n">
+        <v>20</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>29/12/25: Desde 04/09/25 no setor DTCREDITORIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="n">
+        <v>21</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Processo 70/25 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="n">
+        <v>21</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>29/12/25: Desde 05/09/25 no setor DTCREDITORIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="n">
+        <v>21</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Observação: Valores de diferença de oimpostos ressarcidos pelo agente de carga na origem, pela falha na expedição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="n">
+        <v>22</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Processo 2443/25 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="n">
+        <v>22</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>12/11:  Doc recebido pela RFB. Fase de Preparar Distribuição. Sem intimação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="n">
+        <v>23</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Processo 10529/24 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="n">
+        <v>23</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>29/12/25: Cobrado CS + analista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>23</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Observação: Ajuste NCM, com IPI zerado, após desembaraço</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>24</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Processo 2003/25 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>24</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>29/12/25: Desde 15/10/25 aguardando parecer / despacho</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>24</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Observação: Debito DI na conta cliente. Mas cliente pediu ressarcimento, até restituição. Termo assinado pela SGS em 21/10/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>25</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Processo OC0708/23 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>25</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2025-01-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>03/01/25: Sem acesso ecac</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>25</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Observação: Alterado valor na INVOICE final</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>26</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Processo 1630/25 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>26</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>29/12/25: No setor DTCREDITORIO desde 15/09/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>27</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Processo OE1260/24 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="n">
+        <v>27</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>26/12/25: Ag encaminhamento RFB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="n">
+        <v>28</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Processo 8594/24 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="n">
+        <v>28</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>26/12/25: Em 04/11 direcionado para o setor DTCREDITORIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="n">
+        <v>29</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Processo 13193/24 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="n">
+        <v>29</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>26/12/25: Ag encaminhamento RFB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>30</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Processo 1360/25 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>30</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>29/12/25: Desde 15/09/25 no setor DTCREDITORIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>31</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Processo 13068/24 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>31</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2025-12-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>29/12/25:  Desde 05/08/25 no setor DTCREDITORIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>32</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Processo 5953/25 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>32</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-01-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>13/01/26: Processo protocolado</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>32</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Observação: Emissão de LI incorreto. Sem mencionar ex-tarifário.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>33</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Processo 3831/25 importado com status 'Protocolado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>33</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Observação: Alteração de NCM</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>34</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Processo OC0348/23 importado com status 'Com Pendências'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>34</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>02.12 - Solic CS, posição Ecac com cliente</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>34</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Observação: valor unitário conforme abaixo:  DE: 0,726  PARA: 0,6897</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>35</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Processo OE2213/23 importado com status 'Com Pendências'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>35</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>17/03/26 e 19/0326: Cobrado analista, e instruido docs complementares,</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>36</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Processo OE1517/24 importado com status 'Deferido'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>36</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>18/03/26: Encaminhamento para jurisdição Florianopolis</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>36</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Observação: Não temos contrato de câmbio, sendo assim processo 100%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>37</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Processo OP0703/24 importado com status 'Deferido'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="n">
+        <v>37</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>18/03/26: Desde 10/03 VR-DEVAT09-EQCRE-REST / Eq Exec Dir Cred Restituiçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="n">
+        <v>37</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Observação: 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="n">
+        <v>38</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Processo OP0696/24 importado com status 'Deferido'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="n">
+        <v>38</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>26/12/25: Juntada recebida em 02/12/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="n">
+        <v>38</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Observação: 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="n">
+        <v>39</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Processo OE0710/24 importado com status 'Deferido'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="n">
+        <v>39</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-03-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>18/03/26: 07/11/25 emitido extrato do processo de restituição</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="n">
+        <v>39</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Observação: Retificação aliquota PIS e cofins</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="n">
+        <v>40</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Processo OE0949/24 importado com status 'Deferido'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="n">
+        <v>40</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>26/12/25: Docs recebidos em 08/12/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="n">
+        <v>40</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Observação: 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="n">
+        <v>41</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Processo 291/22 importado com status 'Indeferido'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="n">
+        <v>41</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-02-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>19/02/2026: Pedido indeferido pela fiscal Ingrid. "Solicitação de inclusão de benefício após o desembaraço. Falta do controle aduaneiro para identificação do bem."</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="n">
+        <v>42</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Processo 322/25 importado com status 'Indeferido'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="n">
+        <v>42</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>04/03: Processo INDEFERIDO.   11000721307202521_0000051_0000053_DESPACHO_DECISORIO_20260304_180734.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="n">
+        <v>43</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Processo OE0173/23 importado com status 'Indeferido'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="n">
+        <v>43</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Arquivado por desistência.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="n">
+        <v>43</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-02-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>27/02/26: Nova Intimação recebida:   image.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="n">
+        <v>43</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Observação: Seguro declarado a maior</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="n">
+        <v>44</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Processo OE1752/23 importado com status 'Indeferido'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="n">
+        <v>44</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>INDEFERIDO: A importação foi parametrizada em canal vermelho, mantendo-se a classificação original. Ainda, foi informado que não houve laudo realizado no decorrer do despacho. A retificação foi realizada após o desembaraço.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="n">
+        <v>44</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:46:58</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Observação: Ajustado aliquota IPI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -8007,7 +8007,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deferido</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 22:51:11</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deferido</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 22:51:11</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deferido</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 22:51:11</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deferido</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 22:51:11</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deferido</t>
+          <t>Pago</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 22:51:11</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -8714,7 +8714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11969,6 +11969,146 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="n">
+        <v>36</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:51:11</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Status: Deferido → Pago</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="n">
+        <v>37</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:51:11</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Status: Deferido → Pago</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="n">
+        <v>38</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:51:11</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Status: Deferido → Pago</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="n">
+        <v>39</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:51:11</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Status: Deferido → Pago</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="n">
+        <v>40</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:51:11</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>migração ClickUp</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Status: Deferido → Pago</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46125.70025251157</v>
+        <v>46128.98139359206</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>
@@ -5075,7 +5075,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46128.70413718931</v>
+        <v>46128.7041371875</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>46124.81842873843</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -5419,11 +5419,6 @@
       <c r="I2" t="n">
         <v>12540.83</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Bruno Picinini</t>
-        </is>
-      </c>
       <c r="M2" s="1" t="n">
         <v>45548</v>
       </c>
@@ -5445,12 +5440,12 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:17:17</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>test</t>
         </is>
       </c>
     </row>
@@ -5496,11 +5491,6 @@
       <c r="I3" t="n">
         <v>43837</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Bruno Picinini</t>
-        </is>
-      </c>
       <c r="L3" s="1" t="n">
         <v>45460</v>
       </c>
@@ -5530,12 +5520,12 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:49</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -5799,11 +5789,6 @@
       <c r="I7" t="n">
         <v>11499</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M7" s="1" t="n">
         <v>45196</v>
       </c>
@@ -5827,12 +5812,12 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:49</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -5878,11 +5863,6 @@
       <c r="I8" t="n">
         <v>3169</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M8" s="1" t="n">
         <v>45196</v>
       </c>
@@ -5906,12 +5886,12 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:49</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -5957,11 +5937,6 @@
       <c r="I9" t="n">
         <v>458.6</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M9" s="1" t="n">
         <v>45555</v>
       </c>
@@ -5980,12 +5955,12 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:50</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -6108,11 +6083,6 @@
       <c r="I11" t="n">
         <v>3127.82</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="L11" s="1" t="n">
         <v>45370</v>
       </c>
@@ -6139,12 +6109,12 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:50</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -6190,11 +6160,6 @@
       <c r="I12" t="n">
         <v>33498.89</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Mariana Strick</t>
-        </is>
-      </c>
       <c r="L12" s="1" t="n">
         <v>46125</v>
       </c>
@@ -6221,12 +6186,12 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:50</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -6701,11 +6666,6 @@
       <c r="I19" t="n">
         <v>4382.27</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="L19" s="1" t="n">
         <v>45621</v>
       </c>
@@ -6727,12 +6687,12 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:50</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -6778,11 +6738,6 @@
       <c r="I20" t="n">
         <v>22008.5</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M20" s="1" t="n">
         <v>45121</v>
       </c>
@@ -6806,12 +6761,12 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:50</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -6857,11 +6812,6 @@
       <c r="I21" t="n">
         <v>27607.59</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M21" s="1" t="n">
         <v>45810</v>
       </c>
@@ -6880,12 +6830,12 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:50</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -6931,11 +6881,6 @@
       <c r="I22" t="n">
         <v>1011.81</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="L22" s="1" t="n">
         <v>45845</v>
       </c>
@@ -6957,12 +6902,12 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:50</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -7008,11 +6953,6 @@
       <c r="I23" t="n">
         <v>4175.42</v>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M23" s="1" t="n">
         <v>45825</v>
       </c>
@@ -7036,12 +6976,12 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:50</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -7087,11 +7027,6 @@
       <c r="I24" t="n">
         <v>1233.99</v>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="L24" s="1" t="n">
         <v>45618</v>
       </c>
@@ -7113,12 +7048,12 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:50</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -7164,11 +7099,6 @@
       <c r="I25" t="n">
         <v>34414.57</v>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M25" s="1" t="n">
         <v>45936</v>
       </c>
@@ -7187,12 +7117,12 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:50</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -7238,11 +7168,6 @@
       <c r="I26" t="n">
         <v>6922</v>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M26" s="1" t="n">
         <v>45149</v>
       </c>
@@ -7266,12 +7191,12 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:50</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -7317,11 +7242,6 @@
       <c r="I27" t="n">
         <v>1357.38</v>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M27" s="1" t="n">
         <v>45826</v>
       </c>
@@ -7345,12 +7265,12 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:50</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -7900,11 +7820,6 @@
       <c r="I35" t="n">
         <v>5332</v>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M35" s="1" t="n">
         <v>45050</v>
       </c>
@@ -7928,12 +7843,12 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:51</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -8031,11 +7946,6 @@
       <c r="J37" t="n">
         <v>1956.5</v>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Bruno Picinini</t>
-        </is>
-      </c>
       <c r="L37" s="1" t="n">
         <v>45597</v>
       </c>
@@ -8057,12 +7967,12 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2026-04-16 22:51:11</t>
+          <t>2026-04-16 23:16:51</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -8111,11 +8021,6 @@
       <c r="J38" t="n">
         <v>45540.56</v>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Bruno Picinini</t>
-        </is>
-      </c>
       <c r="L38" s="1" t="n">
         <v>45460</v>
       </c>
@@ -8145,12 +8050,12 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>2026-04-16 22:51:11</t>
+          <t>2026-04-16 23:16:51</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -8199,11 +8104,6 @@
       <c r="J39" t="n">
         <v>63509.24</v>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Bruno Picinini</t>
-        </is>
-      </c>
       <c r="L39" s="1" t="n">
         <v>45460</v>
       </c>
@@ -8233,12 +8133,12 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>2026-04-16 22:51:11</t>
+          <t>2026-04-16 23:16:51</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -8287,11 +8187,6 @@
       <c r="J40" t="n">
         <v>1448.89</v>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M40" s="1" t="n">
         <v>45386</v>
       </c>
@@ -8310,12 +8205,12 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2026-04-16 22:51:11</t>
+          <t>2026-04-16 23:16:51</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -8364,11 +8259,6 @@
       <c r="J41" t="n">
         <v>4196.18</v>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Bruno Picinini</t>
-        </is>
-      </c>
       <c r="L41" s="1" t="n">
         <v>45460</v>
       </c>
@@ -8398,12 +8288,12 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2026-04-16 22:51:11</t>
+          <t>2026-04-16 23:16:51</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -8518,11 +8408,6 @@
       <c r="I43" t="n">
         <v>11562.6</v>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M43" s="1" t="n">
         <v>45685</v>
       </c>
@@ -8541,12 +8426,12 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:51</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -8592,11 +8477,6 @@
       <c r="I44" t="n">
         <v>691</v>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M44" s="1" t="n">
         <v>44994</v>
       </c>
@@ -8620,12 +8500,12 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:51</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -8671,11 +8551,6 @@
       <c r="I45" t="n">
         <v>3619.66</v>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Patrice Zeidler Basso</t>
-        </is>
-      </c>
       <c r="M45" s="1" t="n">
         <v>45404</v>
       </c>
@@ -8694,12 +8569,12 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-16 23:16:51</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12109,6 +11984,734 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:49</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Responsável: Bruno Picinini → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="n">
+        <v>2</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:49</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Responsável: Bruno Picinini → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="n">
+        <v>6</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:49</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="n">
+        <v>7</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:49</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="n">
+        <v>8</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:50</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="n">
+        <v>10</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:50</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="n">
+        <v>11</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:50</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Responsável: Mariana Strick → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="n">
+        <v>18</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:50</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="n">
+        <v>19</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:50</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="n">
+        <v>20</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:50</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="n">
+        <v>21</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:50</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="n">
+        <v>22</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:50</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="n">
+        <v>23</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:50</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>24</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:50</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>25</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:50</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>26</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:50</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>34</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:51</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>36</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:51</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Responsável: Bruno Picinini → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>37</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:51</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Responsável: Bruno Picinini → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>38</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:51</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Responsável: Bruno Picinini → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>39</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:51</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>40</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:51</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Responsável: Bruno Picinini → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>42</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:51</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>43</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:51</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>44</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:16:51</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Responsável: Patrice Zeidler Basso → —</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-04-16 23:17:17</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>edicao</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Responsável: Bruno Picinini → —</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -5540,7 +5540,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Winning Plastics</t>
+          <t>WINNING PLASTICS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBR DI 24/0157048-8</t>
+          <t>IBR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>JULIAN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cortexa</t>
+          <t>CORTEXA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eliseu Kopp</t>
+          <t>ELISEU KOPP</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palagi</t>
+          <t>PALAGI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sankem</t>
+          <t>SANKEM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Infortel</t>
+          <t>INFORTEL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Aplinta</t>
+          <t>APLINTA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UNIPELLI 00.596.161/0005-13</t>
+          <t>UNIPELLI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CO3 - DAKEN -</t>
+          <t>CO3 - DAKEN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MH 30.511.579/0001-18</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>MEGA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Winning (academia)</t>
+          <t>WINNING (ACADEMIA)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -5632,6 +5632,11 @@
           <t>Winning</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3S</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>40647.65</v>
       </c>
@@ -6201,7 +6206,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1472/23 / MAHINDRA</t>
+          <t>1472/23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MAHINDRA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6268,7 +6278,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1480/23 / MAHINDRA</t>
+          <t>1480/23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MAHINDRA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -5980,7 +5980,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WINNING/VOLCOM</t>
+          <t>VOLCOM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-17 17:39:23</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>Bruno Picinini</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12727,6 +12727,34 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>9</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:39:23</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-04-17 17:39:23</t>
+          <t>2026-04-16 22:46:58</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Bruno Picinini</t>
+          <t>migração ClickUp</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12727,34 +12727,6 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" t="n">
-        <v>9</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2026-04-17 17:39:23</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Bruno Picinini</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>comentario</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Teste</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46128.98139358796</v>
+        <v>46129.85067406698</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -16,6 +16,8 @@
     <sheet name="Usuarios" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Restituicoes" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="RestituicoesLog" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="ProcessosJudiciais" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ProcessosJudiciaisLog" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -486,6 +488,1451 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>titulo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo_processo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>parte_contraria</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cliente</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>numero_processo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prazo_fatal</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>data_maturacao</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>criado_em</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>criado_por</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>atualizado_em</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>atualizado_por</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Demurrage devido à alteração no POD para Paranaguá</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EXTRAJUDICIAL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CRONOS / TPA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>STRA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OC0978/23</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Encerrado</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>112958</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Metaperfil - RADAR suspenso e reativado na modalidade expressa</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EXTRAJUDICIAL</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Encerrado</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>STRA - Exigência do MAPA para registro do importador</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EXTRAJUDICIAL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Encerrado</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Intimação ref. AT Borche</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO (ECAC)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RFB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BORCHE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>11065.733039/2025-35</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Encerrado</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>55000</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ICMS errado na Estimativa de Custos (redução para 8,8%)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EXTRAJUDICIAL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MAT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MAT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2768/25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Encerrado</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Intimação ref. Ganchos do Uruguai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO (ECAC)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RFB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>WINNING</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10265.487828/2024-99</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Encerrado</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Intimação ref. Pecora</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO (ECAC)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RFB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WINNING/PECORA</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10240.720629/2024-86</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Encerrado</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Intimação ref. CCTs fora do prazo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO (ECAC)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RFB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LEADERLOG</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>13032.615287/2025-16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Encerrado</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>115000</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>45908</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Intimação ref. painés solares ENPHASE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO (ECAC)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RFB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ENR/ENPHASE/WT ENERGY</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10494.722303-2025-92; 10494.722386/2025-10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Encerrado</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>45918</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Intimação ref. Valenacere / World Prime / Minami</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO (ECAC)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RFB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>WINNING</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10494.722694/2025-45; 13033.225502/2024-91</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Encerrado</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>18760000</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>45952</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Intimação ref. Motores</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ADMINISTRATIVO (ECAC)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RFB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ASTON</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>13032.100174/2026-93</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Intimação Pendente</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>8574.1</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Perda de cobertura de seguro, CNPJs fora da Apólice</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>JUDICIAL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BREGALDA E SOMPO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BHIO E INSTRUSUL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OE0032/24; OE0283/24; OE0284/24</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Judicializado</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>processo_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>data_hora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Processo OC0978/23 importado com status 'Encerrado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>17/06 - Dívida quitada pelo cliente no valor de R$ 20.646,85 e contrato assinado. Encerrado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Processo — importado com status 'Encerrado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DI registrada sem cobertura cambial como solução paliativa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Processo — importado com status 'Encerrado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Em andamento na esfera administrativa, sem necessidade de escalar ao jurídico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Processo 11065.733039/2025-35 importado com status 'Encerrado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>04/12 - Multas recolhidas. Intimação respondida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Processo 2768/25 importado com status 'Encerrado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>21/08 - Contranotificação enviada ao cliente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Processo 10265.487828/2024-99 importado com status 'Encerrado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>28/02/25 - Intimação respondida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Processo 10240.720629/2024-86 importado com status 'Encerrado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>11/03/24 - Intimações respondidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Processo 13032.615287/2025-16 importado com status 'Encerrado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>08/09/25 - Intimação respondida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Processo 10494.722303-2025-92; 10494.722386/2025-10 importado com status 'Encerrado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>17/09/25 - Intimações respondidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Processo 10494.722694/2025-45; 13033.225502/2024-91 importado com status 'Encerrado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>22/10 - Intimações respondidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Processo 13032.100174/2026-93 importado com status 'Intimação Pendente'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>migração</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Processo OE0032/24; OE0283/24; OE0284/24 importado com status 'Judicializado'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-04-17 21:24:14</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>27/01 - Vencemos o processo por decurso de prazo. Aguardando intimação para pagamento em 15 dias úteis.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5031,7 +6478,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46129.85067406698</v>
+        <v>46129.8506740625</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -857,7 +857,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Etapa Finalizada</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-17 21:24:14</t>
+          <t>2026-04-17 22:02:34</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>migração</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Etapa Finalizada</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-17 21:24:14</t>
+          <t>2026-04-17 22:02:34</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>migração</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Etapa Finalizada</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -988,12 +988,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-17 21:24:14</t>
+          <t>2026-04-17 22:02:34</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>migração</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Etapa Finalizada</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-17 21:24:14</t>
+          <t>2026-04-17 22:02:35</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>migração</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Encerrado</t>
+          <t>Etapa Finalizada</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-17 21:24:14</t>
+          <t>2026-04-17 22:02:35</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>migração</t>
+          <t>sistema</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1925,6 +1925,146 @@
       <c r="F24" t="inlineStr">
         <is>
           <t>27/01 - Vencemos o processo por decurso de prazo. Aguardando intimação para pagamento em 15 dias úteis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-04-17 22:02:34</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Status: Encerrado → Etapa Finalizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-04-17 22:02:34</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Status: Encerrado → Etapa Finalizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-04-17 22:02:34</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Status: Encerrado → Etapa Finalizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-04-17 22:02:35</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Status: Encerrado → Etapa Finalizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>10</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-04-17 22:02:35</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>sistema</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Status: Encerrado → Etapa Finalizada</t>
         </is>
       </c>
     </row>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -2590,7 +2590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5150,6 +5150,50 @@
       <c r="K63" t="inlineStr">
         <is>
           <t>Ativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Beatriz Ferraz</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>7</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Itajaí</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Itajaí</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Ana Luiza Silva</t>
+        </is>
+      </c>
+      <c r="I64" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Ana Luiza Silva</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5877,6 +5921,37 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>Licença maternidade a partir de fevereiro/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>63</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Beatriz Ferraz</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Entrada</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Assistente</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Contratação registrada em 20/04/2026</t>
         </is>
       </c>
     </row>
@@ -5927,7 +6002,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>24.05</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="3">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Intimação Pendente</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-17 21:24:14</t>
+          <t>2026-04-20 20:30:31</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>migração</t>
+          <t>Bruno Picinini</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2065,6 +2065,34 @@
       <c r="F29" t="inlineStr">
         <is>
           <t>Status: Encerrado → Etapa Finalizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>11</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:30:31</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Status: Intimação Pendente → Encerrado</t>
         </is>
       </c>
     </row>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -1171,7 +1171,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-20 20:30:31</t>
+          <t>2026-04-20 20:30:33</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2093,6 +2093,34 @@
       <c r="F30" t="inlineStr">
         <is>
           <t>Status: Intimação Pendente → Encerrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:30:33</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Retificações registradas e Intimação cumprida.</t>
         </is>
       </c>
     </row>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -1171,7 +1171,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-20 20:30:33</t>
+          <t>2026-04-20 20:30:57</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2119,6 +2119,34 @@
         </is>
       </c>
       <c r="F31" t="inlineStr">
+        <is>
+          <t>Retificações registradas e Intimação cumprida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:30:57</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Retificações registradas e Intimação cumprida.</t>
         </is>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -7365,7 +7365,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Intimação Respondida</t>
+          <t>Intimação Pendente</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-04-16 22:46:58</t>
+          <t>2026-04-22 23:02:13</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>migração ClickUp</t>
+          <t>Bruno Picinini</t>
         </is>
       </c>
     </row>
@@ -10350,7 +10350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14473,6 +14473,34 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>4</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-04-22 23:02:13</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Status: Intimação Respondida → Intimação Pendente</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -7412,7 +7412,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-04-22 23:02:13</t>
+          <t>2026-04-22 23:02:15</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -10350,7 +10350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14501,6 +14501,34 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>4</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-04-22 23:02:15</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Pedido indeferido. Reabrir em nome da Matriz.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1235,6 +1235,67 @@
       <c r="N13" t="inlineStr">
         <is>
           <t>migração</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>COs Valemaste</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RFB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MAVE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10265.161339/2026-71</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Intimação Pendente</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-04-22 23:53:30</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-04-22 23:53:30</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2149,6 +2210,34 @@
       <c r="F32" t="inlineStr">
         <is>
           <t>Retificações registradas e Intimação cumprida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>13</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-04-22 23:53:30</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Processo 10265.161339/2026-71 criado com status 'Intimação Pendente'.</t>
         </is>
       </c>
     </row>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -7682,7 +7682,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Judicializado</t>
+          <t>Intimação Pendente</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -7726,12 +7726,12 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-04-16 23:16:49</t>
+          <t>2026-04-24 19:46:48</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>sistema</t>
+          <t>Bruno Picinini</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14618,6 +14618,34 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>7</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-04-24 19:46:48</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Status: Judicializado → Intimação Pendente</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -7726,7 +7726,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-04-24 19:46:48</t>
+          <t>2026-04-24 19:46:50</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -10439,7 +10439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14646,6 +14646,41 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>7</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-04-24 19:46:50</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>comentario</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>. Nota (s) fiscal (is) de entrada e de saída (DANFE) das mercadorias importadas referentes
+à DI em referência, informando eventuais devoluções, estornos ou cancelamentos.
+2. Declaração do responsável pela empresa informando se os tributos/contribuições foram
+ou não objeto de outro pedido de restituição, de ação judicial e/ou de compensação nem
+integram pedido de compensação eletrônica (DCOMP), bem como se houve ou não
+transferência do encargo a terceiros dos valores relativos aos tributos cuja restituição se
+pleiteia.
+3. Telas da EFD-Contribuições, referentes aos créditos pleiteados.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -2252,7 +2252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2750,6 +2750,25 @@
       </c>
       <c r="E27" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>35</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Analista Júnior</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2763,7 +2782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4425,7 +4444,7 @@
         </is>
       </c>
       <c r="I41" s="1" t="n">
-        <v>43831</v>
+        <v>45689</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -4503,7 +4522,7 @@
         </is>
       </c>
       <c r="I43" s="1" t="n">
-        <v>43831</v>
+        <v>45992</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -4542,7 +4561,7 @@
         </is>
       </c>
       <c r="I44" s="1" t="n">
-        <v>43831</v>
+        <v>45992</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -4581,7 +4600,7 @@
         </is>
       </c>
       <c r="I45" s="1" t="n">
-        <v>43831</v>
+        <v>45962</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4599,7 +4618,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D46" t="n">
         <v>3</v>
@@ -5367,6 +5386,48 @@
       <c r="L64" t="inlineStr">
         <is>
           <t>Ana Luiza Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Morysson</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>35</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Novo Hamburgo</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Novo Hamburgo</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Liliane Maus</t>
+        </is>
+      </c>
+      <c r="I65" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="J65" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Inativo</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6260,6 +6321,174 @@
       </c>
       <c r="D8" t="n">
         <v>24.55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B19" t="n">
+        <v>11</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7.25</v>
       </c>
     </row>
   </sheetData>
@@ -6771,7 +7000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7094,6 +7323,49 @@
       </c>
       <c r="J7" s="2" t="n">
         <v>46125.72053207176</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Liliane Maus</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>liliane.maus@leaderlog.com.br</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Usuário</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ativo</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Home|Organograma|KPIs|Controle de Pessoas</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1b6dc0c0b46a137ffae83f2e27ded229bf0a0bbf227714b92dcc2606242de12b</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>75cc390fd8dca9b6789111ef4821f3c0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>46136.88453359283</v>
       </c>
     </row>
   </sheetData>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -6200,7 +6200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6264,7 +6264,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="5">
@@ -6488,6 +6488,160 @@
         <v>3</v>
       </c>
       <c r="D20" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B29" t="n">
+        <v>10</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B30" t="n">
+        <v>11</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
         <v>7.25</v>
       </c>
     </row>
@@ -7365,7 +7519,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46136.88453359283</v>
+        <v>46136.88453358796</v>
       </c>
     </row>
   </sheetData>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -6110,7 +6110,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Desligamento</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -6120,11 +6120,6 @@
       </c>
       <c r="F27" s="1" t="n">
         <v>46125</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Desligamento registrado em 13/04/2026</t>
-        </is>
       </c>
     </row>
     <row r="28">
@@ -6141,7 +6136,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Licença Maternidade</t>
+          <t>Saída</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6151,11 +6146,6 @@
       </c>
       <c r="F28" s="1" t="n">
         <v>46054</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Licença maternidade a partir de fevereiro/2026</t>
-        </is>
       </c>
     </row>
     <row r="29">

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46129.8506740625</v>
+        <v>46138.73713618965</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1294,6 +1294,62 @@
         </is>
       </c>
       <c r="N14" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Certificados de Origem Arrow</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ARROW</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10265.156592/2026-11</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Intimação Pendente</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-04-27 21:16:21</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-04-27 21:16:21</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Bruno Picinini</t>
         </is>
@@ -1310,7 +1366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2238,6 +2294,34 @@
       <c r="F33" t="inlineStr">
         <is>
           <t>Processo 10265.161339/2026-71 criado com status 'Intimação Pendente'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>14</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-04-27 21:16:21</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Bruno Picinini</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>criacao</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Processo 10265.156592/2026-11 criado com status 'Intimação Pendente'.</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7323,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46138.73713618965</v>
+        <v>46138.73713619213</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>46124.8184281713</v>

--- a/data/dados.xlsx
+++ b/data/dados.xlsx
@@ -18,6 +18,7 @@
     <sheet name="RestituicoesLog" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="ProcessosJudiciais" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="ProcessosJudiciaisLog" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="PerformanceExportacao" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2330,6 +2331,57 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>volume_score</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>manpower</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>performance</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct_meta</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7592,6 +7644,9 @@
           <t>75cc390fd8dca9b6789111ef4821f3c0</t>
         </is>
       </c>
+      <c r="I8" s="2" t="n">
+        <v>46140.50870728391</v>
+      </c>
       <c r="J8" s="2" t="n">
         <v>46136.88453358796</v>
       </c>
